--- a/artfynd/A 22264-2022 artfynd.xlsx
+++ b/artfynd/A 22264-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22264-2022 artfynd.xlsx
+++ b/artfynd/A 22264-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4173766</v>
+        <v>54038522</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>103265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Odlarvallen, O om, Srm</t>
+          <t>Hästmossen, NV om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590827.8123427063</v>
+        <v>590687.5083604231</v>
       </c>
       <c r="R2" t="n">
-        <v>6579030.309507585</v>
+        <v>6579018.782738454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-07</t>
+          <t>2015-06-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-07</t>
+          <t>2015-06-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -772,11 +768,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,7 +779,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog, sphagnumbevuxen kulle</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54038522</v>
+        <v>54038526</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
+        <v>95519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmossen, NV om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590687.5083604231</v>
+        <v>590837.9627052032</v>
       </c>
       <c r="R3" t="n">
-        <v>6579018.782738454</v>
+        <v>6578990.748839545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +896,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54038526</v>
+        <v>54038521</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
+        <v>95522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -968,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590837.9627052032</v>
+        <v>590687.5083604231</v>
       </c>
       <c r="R4" t="n">
-        <v>6578990.748839545</v>
+        <v>6579018.782738454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,7 +1013,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54038521</v>
+        <v>61604704</v>
       </c>
       <c r="B5" t="n">
         <v>95522</v>
@@ -1081,14 +1067,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästmossen, NV om, Srm</t>
+          <t>Odlarvallen, O om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590687.5083604231</v>
+        <v>590707.678048833</v>
       </c>
       <c r="R5" t="n">
-        <v>6579018.782738454</v>
+        <v>6579009.059563161</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1101,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-07</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1125,7 +1111,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-07</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1144,7 +1130,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog, gles</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1162,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61604704</v>
+        <v>72008512</v>
       </c>
       <c r="B6" t="n">
-        <v>95522</v>
+        <v>95519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,16 +1164,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,14 +1184,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Odlarvallen, O om, Srm</t>
+          <t>Torntorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590707.678048833</v>
+        <v>590837.7303093848</v>
       </c>
       <c r="R6" t="n">
-        <v>6579009.059563161</v>
+        <v>6579000.439171648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1218,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1242,7 +1228,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1261,7 +1247,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallskog, gles</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1279,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72008512</v>
+        <v>100743100</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
+        <v>90676</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,41 +1277,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Torntorp, V om, Srm</t>
+          <t>Odlarvallen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590837.7303093848</v>
+        <v>590531.9007895819</v>
       </c>
       <c r="R7" t="n">
-        <v>6579000.439171648</v>
+        <v>6579005.87474707</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1339,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1359,7 +1349,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1375,31 +1365,30 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering (NVI) inför utbyggnad av regionnätet i Eskilstuna kommun </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100743100</v>
+        <v>100743101</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
+        <v>90665</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,25 +1397,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1440,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590531.9007895819</v>
+        <v>590507.2927576459</v>
       </c>
       <c r="R8" t="n">
-        <v>6579005.87474707</v>
+        <v>6578987.425869348</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1516,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100743101</v>
+        <v>100743132</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
+        <v>8377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1556,14 +1545,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Odlarvallen, Srm</t>
+          <t>Torntorp, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590507.2927576459</v>
+        <v>590964.2681634396</v>
       </c>
       <c r="R9" t="n">
-        <v>6578987.425869348</v>
+        <v>6578989.187221647</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1625,7 +1614,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1636,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100743132</v>
+        <v>100743083</v>
       </c>
       <c r="B10" t="n">
-        <v>8377</v>
+        <v>90676</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,25 +1637,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1676,17 +1665,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torntorp, Srm</t>
+          <t>Odlarvallen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590964.2681634396</v>
+        <v>590490.7015577388</v>
       </c>
       <c r="R10" t="n">
-        <v>6578989.187221647</v>
+        <v>6578954.369522976</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1745,7 +1734,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1756,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100743083</v>
+        <v>100743090</v>
       </c>
       <c r="B11" t="n">
         <v>90676</v>
@@ -1800,13 +1789,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590490.7015577388</v>
+        <v>590669.0509082304</v>
       </c>
       <c r="R11" t="n">
-        <v>6578954.369522976</v>
+        <v>6579063.757867686</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1865,7 +1854,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Staffan Roos</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1876,7 +1865,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100743090</v>
+        <v>100743089</v>
       </c>
       <c r="B12" t="n">
         <v>90676</v>
@@ -1920,13 +1909,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590669.0509082304</v>
+        <v>590516.791895441</v>
       </c>
       <c r="R12" t="n">
-        <v>6579063.757867686</v>
+        <v>6579017.761000686</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1985,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Staffan Roos</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1996,7 +1985,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100743089</v>
+        <v>100743103</v>
       </c>
       <c r="B13" t="n">
         <v>90676</v>
@@ -2040,13 +2029,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590516.791895441</v>
+        <v>590493.6939467426</v>
       </c>
       <c r="R13" t="n">
-        <v>6579017.761000686</v>
+        <v>6578957.502894192</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2105,7 +2094,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2116,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100743103</v>
+        <v>104533729</v>
       </c>
       <c r="B14" t="n">
-        <v>90676</v>
+        <v>103265</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,45 +2117,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Odlarvallen, Srm</t>
+          <t>Hästmossen, NV om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590493.6939467426</v>
+        <v>590787.438491941</v>
       </c>
       <c r="R14" t="n">
-        <v>6578957.502894192</v>
+        <v>6579029.851868559</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2190,7 +2184,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2200,7 +2194,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2216,149 +2210,24 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering (NVI) inför utbyggnad av regionnätet i Eskilstuna kommun </t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>104533729</v>
-      </c>
-      <c r="B15" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Hästmossen, NV om, Srm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>590787.438491941</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6579029.851868559</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Stenkvista</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
           <t>Håkan Gustafson</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
